--- a/data/nzd0049/nzd0049.xlsx
+++ b/data/nzd0049/nzd0049.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G604"/>
+  <dimension ref="A1:G609"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16740,6 +16740,141 @@
         <v>372.98</v>
       </c>
       <c r="G604" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B605" t="n">
+        <v>402.41</v>
+      </c>
+      <c r="C605" t="n">
+        <v>372.01</v>
+      </c>
+      <c r="D605" t="n">
+        <v>371.92</v>
+      </c>
+      <c r="E605" t="n">
+        <v>369.09</v>
+      </c>
+      <c r="F605" t="n">
+        <v>372.86</v>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B606" t="n">
+        <v>400.83</v>
+      </c>
+      <c r="C606" t="n">
+        <v>372.4</v>
+      </c>
+      <c r="D606" t="n">
+        <v>372.05</v>
+      </c>
+      <c r="E606" t="n">
+        <v>369.72</v>
+      </c>
+      <c r="F606" t="n">
+        <v>373.52</v>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:17:03+00:00</t>
+        </is>
+      </c>
+      <c r="B607" t="n">
+        <v>395.85</v>
+      </c>
+      <c r="C607" t="n">
+        <v>373.15</v>
+      </c>
+      <c r="D607" t="n">
+        <v>372.39</v>
+      </c>
+      <c r="E607" t="n">
+        <v>370.48</v>
+      </c>
+      <c r="F607" t="n">
+        <v>373.82</v>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B608" t="n">
+        <v>394.58</v>
+      </c>
+      <c r="C608" t="n">
+        <v>373.35</v>
+      </c>
+      <c r="D608" t="n">
+        <v>372.7</v>
+      </c>
+      <c r="E608" t="n">
+        <v>371.23</v>
+      </c>
+      <c r="F608" t="n">
+        <v>374.05</v>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B609" t="n">
+        <v>390.09</v>
+      </c>
+      <c r="C609" t="n">
+        <v>374.29</v>
+      </c>
+      <c r="D609" t="n">
+        <v>372.97</v>
+      </c>
+      <c r="E609" t="n">
+        <v>371.26</v>
+      </c>
+      <c r="F609" t="n">
+        <v>374.33</v>
+      </c>
+      <c r="G609" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -16756,7 +16891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B639"/>
+  <dimension ref="A1:B644"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23149,6 +23284,56 @@
       </c>
       <c r="B639" t="n">
         <v>0.87</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B640" t="n">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B641" t="n">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B642" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B643" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B644" t="n">
+        <v>-0.58</v>
       </c>
     </row>
   </sheetData>
@@ -23317,28 +23502,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5883811063951375</v>
+        <v>-0.6209723496487255</v>
       </c>
       <c r="J2" t="n">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="K2" t="n">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02033447985492354</v>
+        <v>0.02289477133208506</v>
       </c>
       <c r="M2" t="n">
-        <v>26.97311479467404</v>
+        <v>26.91318223874008</v>
       </c>
       <c r="N2" t="n">
-        <v>979.353098544032</v>
+        <v>975.059872335371</v>
       </c>
       <c r="O2" t="n">
-        <v>31.29461772484259</v>
+        <v>31.22594870192691</v>
       </c>
       <c r="P2" t="n">
-        <v>433.7995620369558</v>
+        <v>434.14194646224</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23395,28 +23580,28 @@
         <v>0.0673</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1633022544390652</v>
+        <v>-0.1679075853595432</v>
       </c>
       <c r="J3" t="n">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="K3" t="n">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1810956787515151</v>
+        <v>0.1904513193500024</v>
       </c>
       <c r="M3" t="n">
-        <v>2.083447165964731</v>
+        <v>2.089447596293928</v>
       </c>
       <c r="N3" t="n">
-        <v>7.118805193377342</v>
+        <v>7.138233951972175</v>
       </c>
       <c r="O3" t="n">
-        <v>2.668108917075414</v>
+        <v>2.671747359308544</v>
       </c>
       <c r="P3" t="n">
-        <v>380.4505258746232</v>
+        <v>380.4986965887637</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23473,28 +23658,28 @@
         <v>0.1342</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02209241731299021</v>
+        <v>0.01594807258394322</v>
       </c>
       <c r="J4" t="n">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="K4" t="n">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004580192847706055</v>
+        <v>0.002383433582595407</v>
       </c>
       <c r="M4" t="n">
-        <v>1.992796749402351</v>
+        <v>2.013206883954693</v>
       </c>
       <c r="N4" t="n">
-        <v>6.261907714714127</v>
+        <v>6.341152048371209</v>
       </c>
       <c r="O4" t="n">
-        <v>2.502380409672783</v>
+        <v>2.518164420440256</v>
       </c>
       <c r="P4" t="n">
-        <v>375.8319635292821</v>
+        <v>375.8962399685409</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23551,28 +23736,28 @@
         <v>0.0914</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.03086806561946719</v>
+        <v>-0.03761180940672096</v>
       </c>
       <c r="J5" t="n">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="K5" t="n">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00715868935709385</v>
+        <v>0.01055497005008899</v>
       </c>
       <c r="M5" t="n">
-        <v>2.160519779115921</v>
+        <v>2.174676253270409</v>
       </c>
       <c r="N5" t="n">
-        <v>7.801225365624827</v>
+        <v>7.89903941607386</v>
       </c>
       <c r="O5" t="n">
-        <v>2.793067375776107</v>
+        <v>2.810522979104398</v>
       </c>
       <c r="P5" t="n">
-        <v>375.5967156042024</v>
+        <v>375.6672581322367</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23629,28 +23814,28 @@
         <v>0.0531</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0705998352158267</v>
+        <v>-0.07198410310875188</v>
       </c>
       <c r="J6" t="n">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="K6" t="n">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03864011277014368</v>
+        <v>0.04073012686501098</v>
       </c>
       <c r="M6" t="n">
-        <v>2.095455195476893</v>
+        <v>2.085782841587952</v>
       </c>
       <c r="N6" t="n">
-        <v>7.331663646912737</v>
+        <v>7.279962383133821</v>
       </c>
       <c r="O6" t="n">
-        <v>2.70770449770885</v>
+        <v>2.698140541768316</v>
       </c>
       <c r="P6" t="n">
-        <v>376.5229095973844</v>
+        <v>376.5373780007814</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23688,7 +23873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G604"/>
+  <dimension ref="A1:G609"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46031,6 +46216,191 @@
         </is>
       </c>
     </row>
+    <row r="605">
+      <c r="A605" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>-35.01452953151144,173.85916033318134</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>-35.01517377396866,173.85862418561385</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>-35.01588855179704,173.85851634722806</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>-35.016606766996375,173.85860638036652</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>-35.01731202964633,173.85885096046937</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>-35.01452622742671,173.85914348882835</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>-35.0151743833595,173.85862839530483</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>-35.015888535393465,173.85851777188796</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>-35.01660569886591,173.8586131620598</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>-35.01731063994672,173.8588579941899</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:17:03+00:00</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>-35.014515813270776,173.85909039714207</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>-35.01517555526452,173.8586364908646</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>-35.01588849249168,173.85852149792154</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>-35.01660441032705,173.85862134314982</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>-35.01731000826495,173.8588611913355</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>-35.01451315744815,173.85907685769803</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>-35.015175867772456,173.85863864968056</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>-35.01588845337527,173.85852489518743</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>-35.01660313874213,173.85862941659366</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>-35.017309523975534,173.85886364248043</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>-35.01450376795275,173.85902898990662</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>-35.01517733655914,173.85864879611583</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>-35.01588841930605,173.85852785409645</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>-35.01660308787873,173.8586297395314</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>-35.01730893440573,173.85886662648292</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0049/nzd0049.xlsx
+++ b/data/nzd0049/nzd0049.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G609"/>
+  <dimension ref="A1:G612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16877,6 +16877,87 @@
       <c r="G609" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B610" t="n">
+        <v>388.41</v>
+      </c>
+      <c r="C610" t="n">
+        <v>374.78</v>
+      </c>
+      <c r="D610" t="n">
+        <v>373.34</v>
+      </c>
+      <c r="E610" t="n">
+        <v>371.8</v>
+      </c>
+      <c r="F610" t="n">
+        <v>374.56</v>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B611" t="n">
+        <v>387.35</v>
+      </c>
+      <c r="C611" t="n">
+        <v>375.21</v>
+      </c>
+      <c r="D611" t="n">
+        <v>373.61</v>
+      </c>
+      <c r="E611" t="n">
+        <v>372.62</v>
+      </c>
+      <c r="F611" t="n">
+        <v>374.7</v>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B612" t="n">
+        <v>383.92</v>
+      </c>
+      <c r="C612" t="n">
+        <v>375.51</v>
+      </c>
+      <c r="D612" t="n">
+        <v>373.82</v>
+      </c>
+      <c r="E612" t="n">
+        <v>372.84</v>
+      </c>
+      <c r="F612" t="n">
+        <v>375.7</v>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -16891,7 +16972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B644"/>
+  <dimension ref="A1:B647"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23334,6 +23415,36 @@
       </c>
       <c r="B644" t="n">
         <v>-0.58</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B645" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B646" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B647" t="n">
+        <v>0.08</v>
       </c>
     </row>
   </sheetData>
@@ -23502,28 +23613,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6209723496487255</v>
+        <v>-0.6491238660997217</v>
       </c>
       <c r="J2" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="K2" t="n">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02289477133208506</v>
+        <v>0.02509753013924387</v>
       </c>
       <c r="M2" t="n">
-        <v>26.91318223874008</v>
+        <v>26.92013540389726</v>
       </c>
       <c r="N2" t="n">
-        <v>975.059872335371</v>
+        <v>974.8870480996233</v>
       </c>
       <c r="O2" t="n">
-        <v>31.22594870192691</v>
+        <v>31.22318126167837</v>
       </c>
       <c r="P2" t="n">
-        <v>434.14194646224</v>
+        <v>434.4385114727894</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23580,28 +23691,28 @@
         <v>0.0673</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1679075853595432</v>
+        <v>-0.1686393407620385</v>
       </c>
       <c r="J3" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="K3" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1904513193500024</v>
+        <v>0.1932990285206737</v>
       </c>
       <c r="M3" t="n">
-        <v>2.089447596293928</v>
+        <v>2.082854999167513</v>
       </c>
       <c r="N3" t="n">
-        <v>7.138233951972175</v>
+        <v>7.106776189731902</v>
       </c>
       <c r="O3" t="n">
-        <v>2.671747359308544</v>
+        <v>2.665853745000258</v>
       </c>
       <c r="P3" t="n">
-        <v>380.4986965887637</v>
+        <v>380.5063719219009</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23658,28 +23769,28 @@
         <v>0.1342</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01594807258394322</v>
+        <v>0.01346190916030653</v>
       </c>
       <c r="J4" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="K4" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002383433582595407</v>
+        <v>0.0017069263767443</v>
       </c>
       <c r="M4" t="n">
-        <v>2.013206883954693</v>
+        <v>2.018319957059794</v>
       </c>
       <c r="N4" t="n">
-        <v>6.341152048371209</v>
+        <v>6.346415736103377</v>
       </c>
       <c r="O4" t="n">
-        <v>2.518164420440256</v>
+        <v>2.519209347415053</v>
       </c>
       <c r="P4" t="n">
-        <v>375.8962399685409</v>
+        <v>375.9223233793174</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23736,28 +23847,28 @@
         <v>0.0914</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.03761180940672096</v>
+        <v>-0.03963732538384102</v>
       </c>
       <c r="J5" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="K5" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01055497005008899</v>
+        <v>0.01178997981152607</v>
       </c>
       <c r="M5" t="n">
-        <v>2.174676253270409</v>
+        <v>2.173661941962556</v>
       </c>
       <c r="N5" t="n">
-        <v>7.89903941607386</v>
+        <v>7.885274452345045</v>
       </c>
       <c r="O5" t="n">
-        <v>2.810522979104398</v>
+        <v>2.808073085292661</v>
       </c>
       <c r="P5" t="n">
-        <v>375.6672581322367</v>
+        <v>375.6885071400607</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23814,28 +23925,28 @@
         <v>0.0531</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.07198410310875188</v>
+        <v>-0.07163010252726361</v>
       </c>
       <c r="J6" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="K6" t="n">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04073012686501098</v>
+        <v>0.04073138715765601</v>
       </c>
       <c r="M6" t="n">
-        <v>2.085782841587952</v>
+        <v>2.077511579370309</v>
       </c>
       <c r="N6" t="n">
-        <v>7.279962383133821</v>
+        <v>7.246158225582854</v>
       </c>
       <c r="O6" t="n">
-        <v>2.698140541768316</v>
+        <v>2.691868909435014</v>
       </c>
       <c r="P6" t="n">
-        <v>376.5373780007814</v>
+        <v>376.533661338112</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23873,7 +23984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G609"/>
+  <dimension ref="A1:G612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46401,6 +46512,117 @@
         </is>
       </c>
     </row>
+    <row r="610">
+      <c r="A610" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>-35.0145002547291,173.85901107946626</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>-35.01517810220293,173.85865408521522</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>-35.015888372618484,173.8585319088977</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>-35.01660217233722,173.85863555241082</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>-35.017308450116204,173.85886907762782</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>-35.014498038050895,173.85899977883201</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>-35.01517877409423,173.85865872666986</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>-35.0158883385491,173.85853486780667</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>-35.016600782069986,173.85864437937556</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>-35.01730815533126,173.858870569629</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>-35.01449086520754,173.85896321168937</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>-35.015179242855496,173.85866196489408</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>-35.01588831205063,173.85853716918032</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>-35.016600409071344,173.85864674758554</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>-35.017306049723935,173.8588812267802</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0049/nzd0049.xlsx
+++ b/data/nzd0049/nzd0049.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G612"/>
+  <dimension ref="A1:G615"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16958,6 +16958,87 @@
       <c r="G612" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:25+00:00</t>
+        </is>
+      </c>
+      <c r="B613" t="n">
+        <v>379.72</v>
+      </c>
+      <c r="C613" t="n">
+        <v>375.34</v>
+      </c>
+      <c r="D613" t="n">
+        <v>373.67</v>
+      </c>
+      <c r="E613" t="n">
+        <v>372.94</v>
+      </c>
+      <c r="F613" t="n">
+        <v>376.17</v>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B614" t="n">
+        <v>382.77</v>
+      </c>
+      <c r="C614" t="n">
+        <v>375.55</v>
+      </c>
+      <c r="D614" t="n">
+        <v>373.56</v>
+      </c>
+      <c r="E614" t="n">
+        <v>373.27</v>
+      </c>
+      <c r="F614" t="n">
+        <v>376.54</v>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B615" t="n">
+        <v>383.79</v>
+      </c>
+      <c r="C615" t="n">
+        <v>376.3</v>
+      </c>
+      <c r="D615" t="n">
+        <v>373.23</v>
+      </c>
+      <c r="E615" t="n">
+        <v>373.56</v>
+      </c>
+      <c r="F615" t="n">
+        <v>376.34</v>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -16972,7 +17053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B647"/>
+  <dimension ref="A1:B650"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23445,6 +23526,36 @@
       </c>
       <c r="B647" t="n">
         <v>0.08</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B648" t="n">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B649" t="n">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B650" t="n">
+        <v>0.75</v>
       </c>
     </row>
   </sheetData>
@@ -23613,28 +23724,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6491238660997217</v>
+        <v>-0.6806589846436836</v>
       </c>
       <c r="J2" t="n">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="K2" t="n">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02509753013924387</v>
+        <v>0.02763816976710853</v>
       </c>
       <c r="M2" t="n">
-        <v>26.92013540389726</v>
+        <v>26.9422245590796</v>
       </c>
       <c r="N2" t="n">
-        <v>974.8870480996233</v>
+        <v>975.9589915334545</v>
       </c>
       <c r="O2" t="n">
-        <v>31.22318126167837</v>
+        <v>31.24034237221888</v>
       </c>
       <c r="P2" t="n">
-        <v>434.4385114727894</v>
+        <v>434.7721314750865</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23691,28 +23802,28 @@
         <v>0.0673</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1686393407620385</v>
+        <v>-0.1688308525057133</v>
       </c>
       <c r="J3" t="n">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="K3" t="n">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1932990285206737</v>
+        <v>0.1952185435215223</v>
       </c>
       <c r="M3" t="n">
-        <v>2.082854999167513</v>
+        <v>2.074820449365614</v>
       </c>
       <c r="N3" t="n">
-        <v>7.106776189731902</v>
+        <v>7.073116643015632</v>
       </c>
       <c r="O3" t="n">
-        <v>2.665853745000258</v>
+        <v>2.659533162608737</v>
       </c>
       <c r="P3" t="n">
-        <v>380.5063719219009</v>
+        <v>380.5083845902516</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23769,28 +23880,28 @@
         <v>0.1342</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01346190916030653</v>
+        <v>0.010933160009986</v>
       </c>
       <c r="J4" t="n">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="K4" t="n">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0017069263767443</v>
+        <v>0.001131226799962692</v>
       </c>
       <c r="M4" t="n">
-        <v>2.018319957059794</v>
+        <v>2.023696739053547</v>
       </c>
       <c r="N4" t="n">
-        <v>6.346415736103377</v>
+        <v>6.353316045204861</v>
       </c>
       <c r="O4" t="n">
-        <v>2.519209347415053</v>
+        <v>2.520578513993337</v>
       </c>
       <c r="P4" t="n">
-        <v>375.9223233793174</v>
+        <v>375.9489735654568</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23847,28 +23958,28 @@
         <v>0.0914</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.03963732538384102</v>
+        <v>-0.04086246253677082</v>
       </c>
       <c r="J5" t="n">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="K5" t="n">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01178997981152607</v>
+        <v>0.01263225559630055</v>
       </c>
       <c r="M5" t="n">
-        <v>2.173661941962556</v>
+        <v>2.168805951101588</v>
       </c>
       <c r="N5" t="n">
-        <v>7.885274452345045</v>
+        <v>7.855926335496641</v>
       </c>
       <c r="O5" t="n">
-        <v>2.808073085292661</v>
+        <v>2.802842545612693</v>
       </c>
       <c r="P5" t="n">
-        <v>375.6885071400607</v>
+        <v>375.7014146250642</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23925,28 +24036,28 @@
         <v>0.0531</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.07163010252726361</v>
+        <v>-0.07004725717979397</v>
       </c>
       <c r="J6" t="n">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="K6" t="n">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04073138715765601</v>
+        <v>0.0393243351670427</v>
       </c>
       <c r="M6" t="n">
-        <v>2.077511579370309</v>
+        <v>2.075639189857021</v>
       </c>
       <c r="N6" t="n">
-        <v>7.246158225582854</v>
+        <v>7.22562884241688</v>
       </c>
       <c r="O6" t="n">
-        <v>2.691868909435014</v>
+        <v>2.688052983558337</v>
       </c>
       <c r="P6" t="n">
-        <v>376.533661338112</v>
+        <v>376.5169903565511</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23984,7 +24095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G612"/>
+  <dimension ref="A1:G615"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46623,6 +46734,117 @@
         </is>
       </c>
     </row>
+    <row r="613">
+      <c r="A613" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:25+00:00</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>-35.01448208211888,173.85891843560475</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>-35.01517897722412,173.85866012990036</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>-35.015888330978115,173.85853552534203</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>-35.0166002395265,173.85864782404465</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>-35.017305060088155,173.85888623564102</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>-35.014488460315874,173.85895095157005</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>-35.015179305356995,173.8586623966573</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>-35.01588834485825,173.85853431986058</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>-35.01659968002842,173.8586513763596</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>-35.01730428101305,173.85889017878677</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>-35.01449059335028,173.8589618257628</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>-35.01518047725973,173.85867049221798</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>-35.01588838649859,173.85853070341625</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>-35.016599188348216,173.85865449809086</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>-35.017304702134744,173.85888804735663</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
